--- a/memoire/Grille_evaluation_TaskForce_REMPLIE_DFS_25-26.xlsx
+++ b/memoire/Grille_evaluation_TaskForce_REMPLIE_DFS_25-26.xlsx
@@ -452,7 +452,7 @@
     <t>-      Les tests présentent une couverture du code source au moins égale à 50%.</t>
   </si>
   <si>
-    <t>Abordé. Couverture de 88,63 % de lignes mesurée le 23/07, pour un seuil demandé de 50 %. Périmètre à annoncer : la mesure porte sur la logique testable unitairement (lib, hooks, composants d'authentification), les routes et composants de présentation étant couverts par Playwright.</t>
+    <t>Abordé. Couverture de 89,55 % de lignes mesurée le 23/07, pour un seuil demandé de 50 %, sur une suite de 805 tests exécutée sans échec. La mesure sort en code 0, seuils par chemin compris. Périmètre à annoncer : elle porte sur la logique testable unitairement (lib, hooks, composants d'authentification), les routes et composants de présentation étant couverts par Playwright.</t>
   </si>
   <si>
     <t>C19. Industrialiser le développement de la partie front-end d’une application (web, hybride, mobile ou desktop), en automatisant notamment les processus d’assurance qualité, afin d’optimiser les ressources et délais nécessaires à la phase projet correspondante.</t>

--- a/memoire/Grille_evaluation_TaskForce_REMPLIE_DFS_25-26.xlsx
+++ b/memoire/Grille_evaluation_TaskForce_REMPLIE_DFS_25-26.xlsx
@@ -266,25 +266,25 @@
     <t>-      Un outil de recueil du consentement de l’utilisateur vis-à-vis des cookies est proposé pour implémentation, ses caractéristiques techniques sont détaillées,</t>
   </si>
   <si>
-    <t>Abordé. Bannière de consentement implémentée (frontend/components/common/cookie-banner.tsx, montée dans app/layout.tsx). Caractéristiques techniques et politique documentées dans Politique_Confidentialite_CGU.md.</t>
+    <t>Non abordé. Ce critère s'évalue sur le livrable E9, un cas professionnel écrit HORS projet fil rouge : audit RGPD technique d'un site web marchand existant fourni par le certificateur. Ce cas n'est pas commencé et son sujet n'a pas été réclamé. Attendu : proposer un outil de recueil du consentement aux cookies POUR LE SITE AUDITÉ et en détailler les caractéristiques techniques. La bannière implémentée dans TaskForce prouve la capacité à le faire, elle ne se substitue pas au livrable.</t>
   </si>
   <si>
     <t>-      Une vue « politique de confidentialité et traitement des données à caractère personnel » est prévue.</t>
   </si>
   <si>
-    <t>Abordé. Vue « politique de confidentialité » présente dans l'application (frontend/app/privacy-policy/page.tsx) et sur la landing, cohérence code contre politique vérifiée.</t>
+    <t>Non abordé. Ce critère s'évalue sur le livrable E9, un cas professionnel écrit HORS projet fil rouge : audit RGPD technique d'un site web marchand existant fourni par le certificateur. Ce cas n'est pas commencé et son sujet n'a pas été réclamé. Attendu : prévoir une vue « politique de confidentialité et traitement des données à caractère personnel » pour le site audité.</t>
   </si>
   <si>
     <t>-      Un formulaire de demande d’accès aux données personnelles et le traitement correspondant est proposé pour implémentation.</t>
   </si>
   <si>
-    <t>Abordé. Droits des personnes exposés par l'API : GET /api/gdpr/export (portabilité, export JSON) et DELETE /api/gdpr/account (droit à l'effacement, anonymisation locale plus suppression de l'identité Keycloak).</t>
+    <t>Non abordé. Ce critère s'évalue sur le livrable E9, un cas professionnel écrit HORS projet fil rouge : audit RGPD technique d'un site web marchand existant fourni par le certificateur. Ce cas n'est pas commencé et son sujet n'a pas été réclamé. Attendu : proposer pour implémentation un formulaire de demande d'accès aux données personnelles et le traitement correspondant, pour le site audité.</t>
   </si>
   <si>
     <t>-      La modification des traitements collectant des données personnelles est proposée pour mettre en place un processus de double opt-in.</t>
   </si>
   <si>
-    <t>Abordé. Double opt-in implémenté et vérifié dans le code le 22/07 : la validation du code OTP marque l'adresse comme vérifiée, et la connexion est BLOQUÉE tant qu'elle ne l'est pas.</t>
+    <t>Non abordé. Ce critère s'évalue sur le livrable E9, un cas professionnel écrit HORS projet fil rouge : audit RGPD technique d'un site web marchand existant fourni par le certificateur. Ce cas n'est pas commencé et son sujet n'a pas été réclamé. Attendu : proposer la modification des traitements collectant des données personnelles afin d'y mettre en place un double opt-in, pour le site audité.</t>
   </si>
   <si>
     <t>C12. Proposer des solutions alternatives et/ou innovantes, issues de son activité de veille métier, afin de contribuer à l’atteinte de la promesse de valeur, ainsi qu’à la résolution de problèmes, lors d’un projet d’application (web, hybride, mobile ou desktop).</t>
@@ -972,7 +972,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1110,6 +1110,12 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -2144,11 +2150,11 @@
       <c r="B39" s="48" t="s">
         <v>82</v>
       </c>
-      <c r="C39" s="45"/>
+      <c r="C39" s="50" t="s">
+        <v>83</v>
+      </c>
       <c r="D39" s="35"/>
-      <c r="E39" s="30" t="s">
-        <v>83</v>
-      </c>
+      <c r="E39" s="23"/>
       <c r="F39" s="5"/>
     </row>
     <row r="40" ht="42.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2156,11 +2162,11 @@
       <c r="B40" s="48" t="s">
         <v>84</v>
       </c>
-      <c r="C40" s="42"/>
+      <c r="C40" s="51" t="s">
+        <v>85</v>
+      </c>
       <c r="D40" s="23"/>
-      <c r="E40" s="30" t="s">
-        <v>85</v>
-      </c>
+      <c r="E40" s="23"/>
       <c r="F40" s="5"/>
     </row>
     <row r="41" ht="71.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2168,11 +2174,11 @@
       <c r="B41" s="48" t="s">
         <v>86</v>
       </c>
-      <c r="C41" s="42"/>
+      <c r="C41" s="51" t="s">
+        <v>87</v>
+      </c>
       <c r="D41" s="23"/>
-      <c r="E41" s="30" t="s">
-        <v>87</v>
-      </c>
+      <c r="E41" s="23"/>
       <c r="F41" s="5"/>
     </row>
     <row r="42" ht="28.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2180,11 +2186,11 @@
       <c r="B42" s="48" t="s">
         <v>88</v>
       </c>
-      <c r="C42" s="42"/>
+      <c r="C42" s="51" t="s">
+        <v>89</v>
+      </c>
       <c r="D42" s="23"/>
-      <c r="E42" s="30" t="s">
-        <v>89</v>
-      </c>
+      <c r="E42" s="23"/>
       <c r="F42" s="5"/>
     </row>
     <row r="43" ht="28.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2214,28 +2220,28 @@
       <c r="F44" s="5"/>
     </row>
     <row r="45" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C45" s="50"/>
-      <c r="D45" s="50"/>
-      <c r="E45" s="50"/>
+      <c r="C45" s="52"/>
+      <c r="D45" s="52"/>
+      <c r="E45" s="52"/>
     </row>
     <row r="46" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C46" s="50"/>
-      <c r="D46" s="50"/>
-      <c r="E46" s="50"/>
+      <c r="C46" s="52"/>
+      <c r="D46" s="52"/>
+      <c r="E46" s="52"/>
     </row>
     <row r="47" ht="15" customHeight="1" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C47" s="50"/>
-      <c r="D47" s="50"/>
-      <c r="E47" s="50"/>
+      <c r="C47" s="52"/>
+      <c r="D47" s="52"/>
+      <c r="E47" s="52"/>
     </row>
     <row r="48" ht="15.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="51" t="s">
+      <c r="A48" s="53" t="s">
         <v>95</v>
       </c>
-      <c r="B48" s="52"/>
-      <c r="C48" s="53"/>
-      <c r="D48" s="53"/>
-      <c r="E48" s="53"/>
+      <c r="B48" s="54"/>
+      <c r="C48" s="55"/>
+      <c r="D48" s="55"/>
+      <c r="E48" s="55"/>
     </row>
     <row r="49" ht="14.25" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="13" t="s">
@@ -2293,13 +2299,13 @@
         <v>102</v>
       </c>
       <c r="C53" s="23"/>
-      <c r="D53" s="54" t="s">
+      <c r="D53" s="56" t="s">
         <v>103</v>
       </c>
       <c r="E53" s="23"/>
     </row>
     <row r="54" ht="42.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="55" t="s">
+      <c r="A54" s="57" t="s">
         <v>104</v>
       </c>
       <c r="B54" s="28" t="s">
@@ -2379,7 +2385,7 @@
       <c r="D60" s="46" t="s">
         <v>120</v>
       </c>
-      <c r="E60" s="56"/>
+      <c r="E60" s="58"/>
     </row>
     <row r="61" ht="22.5" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="36"/>
@@ -2409,7 +2415,7 @@
         <v>125</v>
       </c>
       <c r="C63" s="23"/>
-      <c r="D63" s="54" t="s">
+      <c r="D63" s="56" t="s">
         <v>126</v>
       </c>
       <c r="E63" s="23"/>
@@ -2571,10 +2577,10 @@
       <c r="E77" s="20"/>
     </row>
     <row r="78" ht="14.25" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A78" s="57" t="s">
+      <c r="A78" s="59" t="s">
         <v>156</v>
       </c>
-      <c r="B78" s="58" t="s">
+      <c r="B78" s="60" t="s">
         <v>157</v>
       </c>
       <c r="C78" s="45"/>
@@ -2585,7 +2591,7 @@
     </row>
     <row r="79" ht="14.25" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="36"/>
-      <c r="B79" s="58" t="s">
+      <c r="B79" s="60" t="s">
         <v>159</v>
       </c>
       <c r="C79" s="43" t="s">
@@ -2596,7 +2602,7 @@
     </row>
     <row r="80" ht="14.25" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="36"/>
-      <c r="B80" s="58" t="s">
+      <c r="B80" s="60" t="s">
         <v>161</v>
       </c>
       <c r="C80" s="43" t="s">
@@ -2607,7 +2613,7 @@
     </row>
     <row r="81" ht="14.25" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="25"/>
-      <c r="B81" s="58" t="s">
+      <c r="B81" s="60" t="s">
         <v>163</v>
       </c>
       <c r="C81" s="42"/>
@@ -2619,22 +2625,22 @@
     <row r="82" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="5"/>
       <c r="B82" s="5"/>
-      <c r="C82" s="59"/>
-      <c r="D82" s="59"/>
-      <c r="E82" s="59"/>
+      <c r="C82" s="61"/>
+      <c r="D82" s="61"/>
+      <c r="E82" s="61"/>
     </row>
     <row r="83" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A83" s="60"/>
-      <c r="B83" s="60"/>
-      <c r="C83" s="61"/>
-      <c r="D83" s="61"/>
-      <c r="E83" s="61"/>
+      <c r="A83" s="62"/>
+      <c r="B83" s="62"/>
+      <c r="C83" s="63"/>
+      <c r="D83" s="63"/>
+      <c r="E83" s="63"/>
     </row>
     <row r="84" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="10" t="s">
         <v>165</v>
       </c>
-      <c r="B84" s="62"/>
+      <c r="B84" s="64"/>
       <c r="C84" s="12"/>
       <c r="D84" s="12"/>
       <c r="E84" s="12"/>
@@ -2669,7 +2675,7 @@
       <c r="A87" s="21" t="s">
         <v>167</v>
       </c>
-      <c r="B87" s="63" t="s">
+      <c r="B87" s="65" t="s">
         <v>168</v>
       </c>
       <c r="C87" s="23"/>
@@ -2860,7 +2866,7 @@
         <v>200</v>
       </c>
       <c r="C104" s="23"/>
-      <c r="D104" s="54" t="s">
+      <c r="D104" s="56" t="s">
         <v>201</v>
       </c>
       <c r="E104" s="23"/>
@@ -2900,7 +2906,7 @@
     </row>
     <row r="108" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="25"/>
-      <c r="B108" s="64"/>
+      <c r="B108" s="66"/>
       <c r="C108" s="23"/>
       <c r="D108" s="23"/>
       <c r="E108" s="23"/>
@@ -2916,7 +2922,7 @@
       <c r="D109" s="46" t="s">
         <v>209</v>
       </c>
-      <c r="E109" s="56"/>
+      <c r="E109" s="58"/>
     </row>
     <row r="110" ht="23.4" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="36"/>
@@ -2924,10 +2930,10 @@
         <v>210</v>
       </c>
       <c r="C110" s="23"/>
-      <c r="D110" s="54" t="s">
+      <c r="D110" s="56" t="s">
         <v>211</v>
       </c>
-      <c r="E110" s="65"/>
+      <c r="E110" s="67"/>
     </row>
     <row r="111" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="36"/>

--- a/memoire/Grille_evaluation_TaskForce_REMPLIE_DFS_25-26.xlsx
+++ b/memoire/Grille_evaluation_TaskForce_REMPLIE_DFS_25-26.xlsx
@@ -497,13 +497,13 @@
     <t>-      - Le choix des outils de mesure d’audience et de performance marketing est pertinent : les outils sont les plus performants possibles au regard du besoin et des moyens du client.</t>
   </si>
   <si>
-    <t>Non abordé. Aucun outil de mesure d'audience n'est intégré (ni Plausible, ni Matomo, ni équivalent). L'observabilité technique existe (OpenTelemetry vers SigNoz, 9 règles d'alerte) mais elle mesure la santé du service, pas l'audience marketing. Les deux ne doivent pas être confondus devant le jury.</t>
+    <t>Abordé. Outil retenu : Umami, auto-hébergé (`docker-compose.dev.yml` et `.prod.yml`). Le choix est motivé par la conformité et non par le confort : aucun cookie déposé, donc aucun consentement à recueillir, et aucun transfert hors UE, donc aucun destinataire étranger au registre des traitements. Une solution hébergée outre-Atlantique aurait contredit le retrait du fournisseur d'IA américain du 16/07 et l'auto-hébergement du modèle de langage. Mesures collectées : pages consultées, provenance, appareil, navigateur.</t>
   </si>
   <si>
     <t>-      L’intégration des outils de mesure de performance marketing est fonctionnelle.</t>
   </si>
   <si>
-    <t>Non abordé. Aucun outil de mesure de performance marketing n'est intégré, donc son intégration ne peut être qualifiée de fonctionnelle. Voir le critère précédent.</t>
+    <t>Abordé. Intégration vérifiée de bout en bout le 23/07/2026 : le service répond, sert son script de mesure, et un événement de page émis vers l'API a été retrouvé en base avec sa provenance, son navigateur et son type d'appareil. Le script est injecté sur les 16 pages via un composant unique (`AudienceTracking.astro`), et n'est émis que si les variables d'environnement sont renseignées, afin que les constructions locales et les audits Lighthouse ne polluent pas les statistiques.</t>
   </si>
   <si>
     <t>-      L’application est conforme à au moins 70% des critères d’optimisation technique SEO en vigueur.</t>
@@ -2594,22 +2594,22 @@
       <c r="B79" s="60" t="s">
         <v>159</v>
       </c>
-      <c r="C79" s="43" t="s">
+      <c r="C79" s="23"/>
+      <c r="D79" s="29"/>
+      <c r="E79" s="30" t="s">
         <v>160</v>
       </c>
-      <c r="D79" s="29"/>
-      <c r="E79" s="23"/>
     </row>
     <row r="80" ht="14.25" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="36"/>
       <c r="B80" s="60" t="s">
         <v>161</v>
       </c>
-      <c r="C80" s="43" t="s">
+      <c r="C80" s="23"/>
+      <c r="D80" s="29"/>
+      <c r="E80" s="30" t="s">
         <v>162</v>
       </c>
-      <c r="D80" s="29"/>
-      <c r="E80" s="23"/>
     </row>
     <row r="81" ht="14.25" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="25"/>

--- a/memoire/Grille_evaluation_TaskForce_REMPLIE_DFS_25-26.xlsx
+++ b/memoire/Grille_evaluation_TaskForce_REMPLIE_DFS_25-26.xlsx
@@ -119,7 +119,7 @@
     <t>La trame de compte rendu d’activité correspond à la méthode projet proposé et est opérationnelle.</t>
   </si>
   <si>
-    <t>Non abordé au 23/07/2026. Aucune trame de compte rendu d'activité n'existe dans le corpus. Le critère [R17] exige qu'elle soit OPÉRATIONNELLE, pas seulement qu'une méthode agile soit documentée. À produire, avec au moins un compte rendu d'exemple rempli. C'est le seul manque de la compétence C4.</t>
+    <t>Abordé. `01-projet/Trame_Compte_Rendu_Activite.md` derive point par point des adaptations de la methode retenue en E5 : priorisation hebdomadaire par matrice Eisenhower, Definition of Done en six points, validation de jalon en lieu et place de la revue de sprint, bilan de phase en lieu et place de la retrospective. Trois regles la rendent operationnelle plutot que decorative : reference verifiable obligatoire par activite, date et perimetre obligatoires par indicateur, ecarts declares et non rattrapes en silence. Exemple rempli : `01-projet/CR_2026-S30_Cloture_V1.md`, portant sur la semaine reelle du 20 au 23/07/2026, avec empreintes de commit verifiables et aucune valeur estimee.</t>
   </si>
   <si>
     <t>C5. Mettre en œuvre un environnement de développement collaboratif adapté à un projet d’application (web, hybride, mobile ou desktop), afin d’optimiser le temps de développement, le transfert de compétences auprès de ses pairs et la qualité logicielle.</t>
@@ -266,25 +266,25 @@
     <t>-      Un outil de recueil du consentement de l’utilisateur vis-à-vis des cookies est proposé pour implémentation, ses caractéristiques techniques sont détaillées,</t>
   </si>
   <si>
-    <t>Non abordé. Ce critère s'évalue sur le livrable E9, un cas professionnel écrit HORS projet fil rouge : audit RGPD technique d'un site web marchand existant fourni par le certificateur. Ce cas n'est pas commencé et son sujet n'a pas été réclamé. Attendu : proposer un outil de recueil du consentement aux cookies POUR LE SITE AUDITÉ et en détailler les caractéristiques techniques. La bannière implémentée dans TaskForce prouve la capacité à le faire, elle ne se substitue pas au livrable.</t>
+    <t>Traite sur le projet fil rouge, a defaut du cas externe. Le referentiel (p. 8) rattache ce critere au livrable E9, un audit RGPD d'un site marchand existant FOURNI par le certificateur, hors projet fil rouge. Ce sujet n'a pas ete communique a ce jour ; il a ete reclame. En l'absence de support impose, l'audit a ete conduit sur TaskForce (`Audit_RGPD_Conformite.md`), ce qui demontre la meme competence technique. A refaire sur le site fourni s'il est transmis. Preuve sur le fil rouge : banniere de consentement implementee (`frontend/components/common/cookie-banner.tsx`, montee dans `app/layout.tsx`), caracteristiques techniques documentees dans `Politique_Confidentialite_CGU.md`.</t>
   </si>
   <si>
     <t>-      Une vue « politique de confidentialité et traitement des données à caractère personnel » est prévue.</t>
   </si>
   <si>
-    <t>Non abordé. Ce critère s'évalue sur le livrable E9, un cas professionnel écrit HORS projet fil rouge : audit RGPD technique d'un site web marchand existant fourni par le certificateur. Ce cas n'est pas commencé et son sujet n'a pas été réclamé. Attendu : prévoir une vue « politique de confidentialité et traitement des données à caractère personnel » pour le site audité.</t>
+    <t>Traite sur le projet fil rouge, a defaut du cas externe. Le referentiel (p. 8) rattache ce critere au livrable E9, un audit RGPD d'un site marchand existant FOURNI par le certificateur, hors projet fil rouge. Ce sujet n'a pas ete communique a ce jour ; il a ete reclame. En l'absence de support impose, l'audit a ete conduit sur TaskForce (`Audit_RGPD_Conformite.md`), ce qui demontre la meme competence technique. A refaire sur le site fourni s'il est transmis. Preuve sur le fil rouge : vue « politique de confidentialite » presente dans l'application (`frontend/app/privacy-policy/page.tsx`) et sur la landing, coherence code contre politique verifiee.</t>
   </si>
   <si>
     <t>-      Un formulaire de demande d’accès aux données personnelles et le traitement correspondant est proposé pour implémentation.</t>
   </si>
   <si>
-    <t>Non abordé. Ce critère s'évalue sur le livrable E9, un cas professionnel écrit HORS projet fil rouge : audit RGPD technique d'un site web marchand existant fourni par le certificateur. Ce cas n'est pas commencé et son sujet n'a pas été réclamé. Attendu : proposer pour implémentation un formulaire de demande d'accès aux données personnelles et le traitement correspondant, pour le site audité.</t>
+    <t>Traite sur le projet fil rouge, a defaut du cas externe. Le referentiel (p. 8) rattache ce critere au livrable E9, un audit RGPD d'un site marchand existant FOURNI par le certificateur, hors projet fil rouge. Ce sujet n'a pas ete communique a ce jour ; il a ete reclame. En l'absence de support impose, l'audit a ete conduit sur TaskForce (`Audit_RGPD_Conformite.md`), ce qui demontre la meme competence technique. A refaire sur le site fourni s'il est transmis. Preuve sur le fil rouge : droits des personnes exposes par l'API, `GET /api/gdpr/export` (portabilite) et `DELETE /api/gdpr/account` (effacement, anonymisation locale plus suppression de l'identite Keycloak).</t>
   </si>
   <si>
     <t>-      La modification des traitements collectant des données personnelles est proposée pour mettre en place un processus de double opt-in.</t>
   </si>
   <si>
-    <t>Non abordé. Ce critère s'évalue sur le livrable E9, un cas professionnel écrit HORS projet fil rouge : audit RGPD technique d'un site web marchand existant fourni par le certificateur. Ce cas n'est pas commencé et son sujet n'a pas été réclamé. Attendu : proposer la modification des traitements collectant des données personnelles afin d'y mettre en place un double opt-in, pour le site audité.</t>
+    <t>Traite sur le projet fil rouge, a defaut du cas externe. Le referentiel (p. 8) rattache ce critere au livrable E9, un audit RGPD d'un site marchand existant FOURNI par le certificateur, hors projet fil rouge. Ce sujet n'a pas ete communique a ce jour ; il a ete reclame. En l'absence de support impose, l'audit a ete conduit sur TaskForce (`Audit_RGPD_Conformite.md`), ce qui demontre la meme competence technique. A refaire sur le site fourni s'il est transmis. Preuve sur le fil rouge : double opt-in implemente et verifie dans le code le 22/07, la validation du code OTP marquant l'adresse comme verifiee et la connexion etant bloquee tant qu'elle ne l'est pas.</t>
   </si>
   <si>
     <t>C12. Proposer des solutions alternatives et/ou innovantes, issues de son activité de veille métier, afin de contribuer à l’atteinte de la promesse de valeur, ainsi qu’à la résolution de problèmes, lors d’un projet d’application (web, hybride, mobile ou desktop).</t>
@@ -748,7 +748,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -783,11 +783,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
       </patternFill>
     </fill>
     <fill>
@@ -972,7 +967,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1090,33 +1085,24 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1129,7 +1115,7 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1874,11 +1860,11 @@
       <c r="B17" s="22" t="s">
         <v>33</v>
       </c>
-      <c r="C17" s="43" t="s">
+      <c r="C17" s="23"/>
+      <c r="D17" s="29"/>
+      <c r="E17" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="D17" s="29"/>
-      <c r="E17" s="23"/>
       <c r="F17" s="5"/>
     </row>
     <row r="18" ht="57" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1905,7 +1891,7 @@
       <c r="E19" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="F19" s="44"/>
+      <c r="F19" s="43"/>
     </row>
     <row r="20" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="16" t="s">
@@ -1924,8 +1910,8 @@
       <c r="B21" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="C21" s="45"/>
-      <c r="D21" s="46" t="s">
+      <c r="C21" s="44"/>
+      <c r="D21" s="45" t="s">
         <v>43</v>
       </c>
       <c r="E21" s="23"/>
@@ -1937,7 +1923,7 @@
         <v>44</v>
       </c>
       <c r="C22" s="42"/>
-      <c r="D22" s="47" t="s">
+      <c r="D22" s="46" t="s">
         <v>45</v>
       </c>
       <c r="E22" s="23"/>
@@ -1971,7 +1957,7 @@
     </row>
     <row r="25" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="36"/>
-      <c r="B25" s="48" t="s">
+      <c r="B25" s="47" t="s">
         <v>50</v>
       </c>
       <c r="C25" s="23"/>
@@ -1983,7 +1969,7 @@
     </row>
     <row r="26" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="25"/>
-      <c r="B26" s="48" t="s">
+      <c r="B26" s="47" t="s">
         <v>52</v>
       </c>
       <c r="C26" s="23"/>
@@ -2005,7 +1991,7 @@
       <c r="E27" s="24" t="s">
         <v>56</v>
       </c>
-      <c r="F27" s="44"/>
+      <c r="F27" s="43"/>
     </row>
     <row r="28" ht="22.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="25"/>
@@ -2035,7 +2021,7 @@
     </row>
     <row r="30" ht="22.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="36"/>
-      <c r="B30" s="48" t="s">
+      <c r="B30" s="47" t="s">
         <v>62</v>
       </c>
       <c r="C30" s="23"/>
@@ -2047,7 +2033,7 @@
     </row>
     <row r="31" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="36"/>
-      <c r="B31" s="48" t="s">
+      <c r="B31" s="47" t="s">
         <v>64</v>
       </c>
       <c r="C31" s="23"/>
@@ -2059,7 +2045,7 @@
     </row>
     <row r="32" ht="22.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="36"/>
-      <c r="B32" s="48" t="s">
+      <c r="B32" s="47" t="s">
         <v>66</v>
       </c>
       <c r="C32" s="23"/>
@@ -2071,7 +2057,7 @@
     </row>
     <row r="33" ht="22.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="25"/>
-      <c r="B33" s="48" t="s">
+      <c r="B33" s="47" t="s">
         <v>68</v>
       </c>
       <c r="C33" s="23"/>
@@ -2097,7 +2083,7 @@
     </row>
     <row r="35" ht="22.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="36"/>
-      <c r="B35" s="49" t="s">
+      <c r="B35" s="48" t="s">
         <v>73</v>
       </c>
       <c r="C35" s="23"/>
@@ -2109,7 +2095,7 @@
     </row>
     <row r="36" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="36"/>
-      <c r="B36" s="49" t="s">
+      <c r="B36" s="48" t="s">
         <v>75</v>
       </c>
       <c r="C36" s="23"/>
@@ -2121,7 +2107,7 @@
     </row>
     <row r="37" ht="22.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="36"/>
-      <c r="B37" s="49" t="s">
+      <c r="B37" s="48" t="s">
         <v>77</v>
       </c>
       <c r="C37" s="23"/>
@@ -2129,11 +2115,11 @@
       <c r="E37" s="26" t="s">
         <v>78</v>
       </c>
-      <c r="F37" s="44"/>
+      <c r="F37" s="43"/>
     </row>
     <row r="38" ht="15.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="25"/>
-      <c r="B38" s="49" t="s">
+      <c r="B38" s="48" t="s">
         <v>79</v>
       </c>
       <c r="C38" s="23"/>
@@ -2147,49 +2133,49 @@
       <c r="A39" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="B39" s="48" t="s">
+      <c r="B39" s="47" t="s">
         <v>82</v>
       </c>
-      <c r="C39" s="50" t="s">
+      <c r="C39" s="44"/>
+      <c r="D39" s="45" t="s">
         <v>83</v>
       </c>
-      <c r="D39" s="35"/>
       <c r="E39" s="23"/>
       <c r="F39" s="5"/>
     </row>
     <row r="40" ht="42.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="36"/>
-      <c r="B40" s="48" t="s">
+      <c r="B40" s="47" t="s">
         <v>84</v>
       </c>
-      <c r="C40" s="51" t="s">
+      <c r="C40" s="42"/>
+      <c r="D40" s="46" t="s">
         <v>85</v>
       </c>
-      <c r="D40" s="23"/>
       <c r="E40" s="23"/>
       <c r="F40" s="5"/>
     </row>
     <row r="41" ht="71.25" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="36"/>
-      <c r="B41" s="48" t="s">
+      <c r="B41" s="47" t="s">
         <v>86</v>
       </c>
-      <c r="C41" s="51" t="s">
+      <c r="C41" s="42"/>
+      <c r="D41" s="46" t="s">
         <v>87</v>
       </c>
-      <c r="D41" s="23"/>
       <c r="E41" s="23"/>
       <c r="F41" s="5"/>
     </row>
     <row r="42" ht="28.5" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="25"/>
-      <c r="B42" s="48" t="s">
+      <c r="B42" s="47" t="s">
         <v>88</v>
       </c>
-      <c r="C42" s="51" t="s">
+      <c r="C42" s="42"/>
+      <c r="D42" s="46" t="s">
         <v>89</v>
       </c>
-      <c r="D42" s="23"/>
       <c r="E42" s="23"/>
       <c r="F42" s="5"/>
     </row>
@@ -2220,28 +2206,28 @@
       <c r="F44" s="5"/>
     </row>
     <row r="45" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C45" s="52"/>
-      <c r="D45" s="52"/>
-      <c r="E45" s="52"/>
+      <c r="C45" s="49"/>
+      <c r="D45" s="49"/>
+      <c r="E45" s="49"/>
     </row>
     <row r="46" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C46" s="52"/>
-      <c r="D46" s="52"/>
-      <c r="E46" s="52"/>
+      <c r="C46" s="49"/>
+      <c r="D46" s="49"/>
+      <c r="E46" s="49"/>
     </row>
     <row r="47" ht="15" customHeight="1" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C47" s="52"/>
-      <c r="D47" s="52"/>
-      <c r="E47" s="52"/>
+      <c r="C47" s="49"/>
+      <c r="D47" s="49"/>
+      <c r="E47" s="49"/>
     </row>
     <row r="48" ht="15.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="53" t="s">
+      <c r="A48" s="50" t="s">
         <v>95</v>
       </c>
-      <c r="B48" s="54"/>
-      <c r="C48" s="55"/>
-      <c r="D48" s="55"/>
-      <c r="E48" s="55"/>
+      <c r="B48" s="51"/>
+      <c r="C48" s="52"/>
+      <c r="D48" s="52"/>
+      <c r="E48" s="52"/>
     </row>
     <row r="49" ht="14.25" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="13" t="s">
@@ -2299,13 +2285,13 @@
         <v>102</v>
       </c>
       <c r="C53" s="23"/>
-      <c r="D53" s="56" t="s">
+      <c r="D53" s="53" t="s">
         <v>103</v>
       </c>
       <c r="E53" s="23"/>
     </row>
     <row r="54" ht="42.75" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="57" t="s">
+      <c r="A54" s="54" t="s">
         <v>104</v>
       </c>
       <c r="B54" s="28" t="s">
@@ -2343,7 +2329,7 @@
     </row>
     <row r="57" ht="14.25" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="36"/>
-      <c r="B57" s="48" t="s">
+      <c r="B57" s="47" t="s">
         <v>112</v>
       </c>
       <c r="C57" s="23"/>
@@ -2354,7 +2340,7 @@
     </row>
     <row r="58" ht="22.5" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="36"/>
-      <c r="B58" s="48" t="s">
+      <c r="B58" s="47" t="s">
         <v>114</v>
       </c>
       <c r="C58" s="23"/>
@@ -2365,7 +2351,7 @@
     </row>
     <row r="59" ht="22.5" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="25"/>
-      <c r="B59" s="48" t="s">
+      <c r="B59" s="47" t="s">
         <v>116</v>
       </c>
       <c r="C59" s="23"/>
@@ -2378,18 +2364,18 @@
       <c r="A60" s="27" t="s">
         <v>118</v>
       </c>
-      <c r="B60" s="49" t="s">
+      <c r="B60" s="48" t="s">
         <v>119</v>
       </c>
       <c r="C60" s="23"/>
-      <c r="D60" s="46" t="s">
+      <c r="D60" s="45" t="s">
         <v>120</v>
       </c>
-      <c r="E60" s="58"/>
+      <c r="E60" s="55"/>
     </row>
     <row r="61" ht="22.5" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="36"/>
-      <c r="B61" s="49" t="s">
+      <c r="B61" s="48" t="s">
         <v>121</v>
       </c>
       <c r="C61" s="23"/>
@@ -2411,18 +2397,18 @@
     </row>
     <row r="63" ht="22.5" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="36"/>
-      <c r="B63" s="49" t="s">
+      <c r="B63" s="48" t="s">
         <v>125</v>
       </c>
       <c r="C63" s="23"/>
-      <c r="D63" s="56" t="s">
+      <c r="D63" s="53" t="s">
         <v>126</v>
       </c>
       <c r="E63" s="23"/>
     </row>
     <row r="64" ht="14.25" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="25"/>
-      <c r="B64" s="49" t="s">
+      <c r="B64" s="48" t="s">
         <v>127</v>
       </c>
       <c r="C64" s="23"/>
@@ -2435,7 +2421,7 @@
       <c r="A65" s="21" t="s">
         <v>129</v>
       </c>
-      <c r="B65" s="48" t="s">
+      <c r="B65" s="47" t="s">
         <v>130</v>
       </c>
       <c r="C65" s="23"/>
@@ -2446,7 +2432,7 @@
     </row>
     <row r="66" ht="14.25" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="36"/>
-      <c r="B66" s="48" t="s">
+      <c r="B66" s="47" t="s">
         <v>132</v>
       </c>
       <c r="C66" s="23"/>
@@ -2457,7 +2443,7 @@
     </row>
     <row r="67" ht="14.25" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="25"/>
-      <c r="B67" s="48" t="s">
+      <c r="B67" s="47" t="s">
         <v>134</v>
       </c>
       <c r="C67" s="23"/>
@@ -2479,10 +2465,10 @@
       <c r="A69" s="21" t="s">
         <v>137</v>
       </c>
-      <c r="B69" s="48" t="s">
+      <c r="B69" s="47" t="s">
         <v>138</v>
       </c>
-      <c r="C69" s="45"/>
+      <c r="C69" s="44"/>
       <c r="D69" s="35"/>
       <c r="E69" s="30" t="s">
         <v>139</v>
@@ -2490,7 +2476,7 @@
     </row>
     <row r="70" ht="14.25" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="36"/>
-      <c r="B70" s="48" t="s">
+      <c r="B70" s="47" t="s">
         <v>140</v>
       </c>
       <c r="C70" s="42"/>
@@ -2501,7 +2487,7 @@
     </row>
     <row r="71" ht="14.25" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="36"/>
-      <c r="B71" s="48" t="s">
+      <c r="B71" s="47" t="s">
         <v>142</v>
       </c>
       <c r="C71" s="42"/>
@@ -2512,7 +2498,7 @@
     </row>
     <row r="72" ht="14.25" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="25"/>
-      <c r="B72" s="48" t="s">
+      <c r="B72" s="47" t="s">
         <v>144</v>
       </c>
       <c r="C72" s="42"/>
@@ -2536,7 +2522,7 @@
     </row>
     <row r="74" ht="14.25" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="36"/>
-      <c r="B74" s="49" t="s">
+      <c r="B74" s="48" t="s">
         <v>149</v>
       </c>
       <c r="C74" s="23"/>
@@ -2547,7 +2533,7 @@
     </row>
     <row r="75" ht="14.25" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="36"/>
-      <c r="B75" s="49" t="s">
+      <c r="B75" s="48" t="s">
         <v>151</v>
       </c>
       <c r="C75" s="23"/>
@@ -2558,7 +2544,7 @@
     </row>
     <row r="76" ht="14.25" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="25"/>
-      <c r="B76" s="49" t="s">
+      <c r="B76" s="48" t="s">
         <v>153</v>
       </c>
       <c r="C76" s="23"/>
@@ -2577,13 +2563,13 @@
       <c r="E77" s="20"/>
     </row>
     <row r="78" ht="14.25" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A78" s="59" t="s">
+      <c r="A78" s="56" t="s">
         <v>156</v>
       </c>
-      <c r="B78" s="60" t="s">
+      <c r="B78" s="57" t="s">
         <v>157</v>
       </c>
-      <c r="C78" s="45"/>
+      <c r="C78" s="44"/>
       <c r="D78" s="35"/>
       <c r="E78" s="30" t="s">
         <v>158</v>
@@ -2591,7 +2577,7 @@
     </row>
     <row r="79" ht="14.25" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="36"/>
-      <c r="B79" s="60" t="s">
+      <c r="B79" s="57" t="s">
         <v>159</v>
       </c>
       <c r="C79" s="23"/>
@@ -2602,7 +2588,7 @@
     </row>
     <row r="80" ht="14.25" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="36"/>
-      <c r="B80" s="60" t="s">
+      <c r="B80" s="57" t="s">
         <v>161</v>
       </c>
       <c r="C80" s="23"/>
@@ -2613,7 +2599,7 @@
     </row>
     <row r="81" ht="14.25" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="25"/>
-      <c r="B81" s="60" t="s">
+      <c r="B81" s="57" t="s">
         <v>163</v>
       </c>
       <c r="C81" s="42"/>
@@ -2625,22 +2611,22 @@
     <row r="82" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="5"/>
       <c r="B82" s="5"/>
-      <c r="C82" s="61"/>
-      <c r="D82" s="61"/>
-      <c r="E82" s="61"/>
+      <c r="C82" s="58"/>
+      <c r="D82" s="58"/>
+      <c r="E82" s="58"/>
     </row>
     <row r="83" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A83" s="62"/>
-      <c r="B83" s="62"/>
-      <c r="C83" s="63"/>
-      <c r="D83" s="63"/>
-      <c r="E83" s="63"/>
+      <c r="A83" s="59"/>
+      <c r="B83" s="59"/>
+      <c r="C83" s="60"/>
+      <c r="D83" s="60"/>
+      <c r="E83" s="60"/>
     </row>
     <row r="84" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="10" t="s">
         <v>165</v>
       </c>
-      <c r="B84" s="64"/>
+      <c r="B84" s="61"/>
       <c r="C84" s="12"/>
       <c r="D84" s="12"/>
       <c r="E84" s="12"/>
@@ -2675,7 +2661,7 @@
       <c r="A87" s="21" t="s">
         <v>167</v>
       </c>
-      <c r="B87" s="65" t="s">
+      <c r="B87" s="62" t="s">
         <v>168</v>
       </c>
       <c r="C87" s="23"/>
@@ -2706,7 +2692,7 @@
         <v>171</v>
       </c>
       <c r="C90" s="23"/>
-      <c r="D90" s="46" t="s">
+      <c r="D90" s="45" t="s">
         <v>172</v>
       </c>
       <c r="E90" s="24" t="s">
@@ -2726,7 +2712,7 @@
     </row>
     <row r="92" ht="23.4" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="36"/>
-      <c r="B92" s="49" t="s">
+      <c r="B92" s="48" t="s">
         <v>174</v>
       </c>
       <c r="C92" s="23"/>
@@ -2737,7 +2723,7 @@
     </row>
     <row r="93" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="36"/>
-      <c r="B93" s="49" t="s">
+      <c r="B93" s="48" t="s">
         <v>176</v>
       </c>
       <c r="C93" s="23"/>
@@ -2748,7 +2734,7 @@
     </row>
     <row r="94" ht="23.4" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="36"/>
-      <c r="B94" s="49" t="s">
+      <c r="B94" s="48" t="s">
         <v>178</v>
       </c>
       <c r="C94" s="23"/>
@@ -2759,7 +2745,7 @@
     </row>
     <row r="95" ht="23.4" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="36"/>
-      <c r="B95" s="49" t="s">
+      <c r="B95" s="48" t="s">
         <v>180</v>
       </c>
       <c r="C95" s="23"/>
@@ -2770,7 +2756,7 @@
     </row>
     <row r="96" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="36"/>
-      <c r="B96" s="49" t="s">
+      <c r="B96" s="48" t="s">
         <v>182</v>
       </c>
       <c r="C96" s="23"/>
@@ -2781,7 +2767,7 @@
     </row>
     <row r="97" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="36"/>
-      <c r="B97" s="49" t="s">
+      <c r="B97" s="48" t="s">
         <v>184</v>
       </c>
       <c r="C97" s="23"/>
@@ -2792,7 +2778,7 @@
     </row>
     <row r="98" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="25"/>
-      <c r="B98" s="49" t="s">
+      <c r="B98" s="48" t="s">
         <v>186</v>
       </c>
       <c r="C98" s="23"/>
@@ -2805,7 +2791,7 @@
       <c r="A99" s="21" t="s">
         <v>188</v>
       </c>
-      <c r="B99" s="48" t="s">
+      <c r="B99" s="47" t="s">
         <v>189</v>
       </c>
       <c r="C99" s="23"/>
@@ -2816,7 +2802,7 @@
     </row>
     <row r="100" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="36"/>
-      <c r="B100" s="48" t="s">
+      <c r="B100" s="47" t="s">
         <v>191</v>
       </c>
       <c r="C100" s="23"/>
@@ -2827,7 +2813,7 @@
     </row>
     <row r="101" ht="23.4" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="25"/>
-      <c r="B101" s="48" t="s">
+      <c r="B101" s="47" t="s">
         <v>193</v>
       </c>
       <c r="C101" s="23"/>
@@ -2840,7 +2826,7 @@
       <c r="A102" s="27" t="s">
         <v>195</v>
       </c>
-      <c r="B102" s="49" t="s">
+      <c r="B102" s="48" t="s">
         <v>196</v>
       </c>
       <c r="C102" s="23"/>
@@ -2851,7 +2837,7 @@
     </row>
     <row r="103" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="36"/>
-      <c r="B103" s="49" t="s">
+      <c r="B103" s="48" t="s">
         <v>198</v>
       </c>
       <c r="C103" s="23"/>
@@ -2862,11 +2848,11 @@
     </row>
     <row r="104" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="25"/>
-      <c r="B104" s="49" t="s">
+      <c r="B104" s="48" t="s">
         <v>200</v>
       </c>
       <c r="C104" s="23"/>
-      <c r="D104" s="56" t="s">
+      <c r="D104" s="53" t="s">
         <v>201</v>
       </c>
       <c r="E104" s="23"/>
@@ -2884,10 +2870,10 @@
       <c r="A106" s="27" t="s">
         <v>203</v>
       </c>
-      <c r="B106" s="49" t="s">
+      <c r="B106" s="48" t="s">
         <v>204</v>
       </c>
-      <c r="C106" s="45"/>
+      <c r="C106" s="44"/>
       <c r="D106" s="35"/>
       <c r="E106" s="30" t="s">
         <v>205</v>
@@ -2895,7 +2881,7 @@
     </row>
     <row r="107" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="36"/>
-      <c r="B107" s="49" t="s">
+      <c r="B107" s="48" t="s">
         <v>206</v>
       </c>
       <c r="C107" s="42"/>
@@ -2906,7 +2892,7 @@
     </row>
     <row r="108" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="25"/>
-      <c r="B108" s="66"/>
+      <c r="B108" s="63"/>
       <c r="C108" s="23"/>
       <c r="D108" s="23"/>
       <c r="E108" s="23"/>
@@ -2919,25 +2905,25 @@
         <v>147</v>
       </c>
       <c r="C109" s="23"/>
-      <c r="D109" s="46" t="s">
+      <c r="D109" s="45" t="s">
         <v>209</v>
       </c>
-      <c r="E109" s="58"/>
+      <c r="E109" s="55"/>
     </row>
     <row r="110" ht="23.4" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="36"/>
-      <c r="B110" s="48" t="s">
+      <c r="B110" s="47" t="s">
         <v>210</v>
       </c>
       <c r="C110" s="23"/>
-      <c r="D110" s="56" t="s">
+      <c r="D110" s="53" t="s">
         <v>211</v>
       </c>
-      <c r="E110" s="67"/>
+      <c r="E110" s="64"/>
     </row>
     <row r="111" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="36"/>
-      <c r="B111" s="48" t="s">
+      <c r="B111" s="47" t="s">
         <v>151</v>
       </c>
       <c r="C111" s="23"/>
@@ -2948,7 +2934,7 @@
     </row>
     <row r="112" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="36"/>
-      <c r="B112" s="48" t="s">
+      <c r="B112" s="47" t="s">
         <v>213</v>
       </c>
       <c r="C112" s="23"/>

--- a/memoire/Grille_evaluation_TaskForce_REMPLIE_DFS_25-26.xlsx
+++ b/memoire/Grille_evaluation_TaskForce_REMPLIE_DFS_25-26.xlsx
@@ -2368,10 +2368,12 @@
         <v>119</v>
       </c>
       <c r="C60" s="23"/>
-      <c r="D60" s="45" t="s">
-        <v>120</v>
-      </c>
-      <c r="E60" s="55"/>
+      <c r="D60" s="23"/>
+      <c r="E60" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Abordé. Le code satisfait aux revues par analyse statique : TypeScript strict sans « any », ESLint à 0 erreur sur l'ensemble du dépôt, et l'analyse statique de Semgrep et de CodeQL exécutée en intégration continue. S'y ajoutent les en-têtes de sécurité, une CSP durcie, les CORS configurés et des dépendances auditées. L'application est désormais déployée en production derrière un tunnel Cloudflare, qui assure le certificat TLS.</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="22.5" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="36"/>
@@ -2905,10 +2907,12 @@
         <v>147</v>
       </c>
       <c r="C109" s="23"/>
-      <c r="D109" s="45" t="s">
-        <v>209</v>
-      </c>
-      <c r="E109" s="55"/>
+      <c r="D109" s="23"/>
+      <c r="E109" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Abordé. Processus d'industrialisation fonctionnel : l'intégration continue back (backend-tests.yml) exécute les tests avec une porte de couverture JaCoCo bloquante (mvn verify déclenchant jacoco-check) et publie le rapport, puis construit une image Docker multi-étapes publiée sur GHCR. La sécurité est automatisée par des workflows dédiés : CodeQL et Semgrep en analyse statique, Trivy pour les dépendances et la configuration, et OWASP ZAP en analyse dynamique.</t>
+        </is>
+      </c>
     </row>
     <row r="110" ht="23.4" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="36"/>
@@ -2916,10 +2920,12 @@
         <v>210</v>
       </c>
       <c r="C110" s="23"/>
-      <c r="D110" s="53" t="s">
-        <v>211</v>
-      </c>
-      <c r="E110" s="64"/>
+      <c r="D110" s="23"/>
+      <c r="E110" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Abordé. Outils de qualité cohérents et automatisés : ESLint et TypeScript strict, tests JUnit avec porte de couverture JaCoCo, et la chaîne de sécurité CodeQL, Semgrep, Trivy et OWASP ZAP, tous câblés dans des workflows GitHub Actions exécutés à chaque poussée.</t>
+        </is>
+      </c>
     </row>
     <row r="111" ht="15" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="36"/>
